--- a/pseudodata/1120.xlsx
+++ b/pseudodata/1120.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,28 +536,28 @@
         <v>0.1</v>
       </c>
       <c r="I2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K2" t="n">
         <v>100</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00134368669109705</v>
+        <v>0.0001802486539502805</v>
       </c>
       <c r="M2" t="n">
-        <v>8.967130046949109e-05</v>
+        <v>0.0003234795269814023</v>
       </c>
       <c r="N2" t="n">
-        <v>6.718433455485249e-05</v>
+        <v>9.012432697514023e-06</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -590,28 +590,28 @@
         <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K3" t="n">
         <v>100</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001339856121875195</v>
+        <v>-2.104595530933435e-05</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001146592568696085</v>
+        <v>0.0003294402681306159</v>
       </c>
       <c r="N3" t="n">
-        <v>6.699280609375975e-05</v>
+        <v>-1.052297765466718e-06</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -644,28 +644,28 @@
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>100</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00103655073435789</v>
+        <v>-0.0002476343798990645</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0001561132841019916</v>
+        <v>0.0003603890239344751</v>
       </c>
       <c r="N4" t="n">
-        <v>5.182753671789452e-05</v>
+        <v>-1.238171899495322e-05</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -698,28 +698,28 @@
         <v>0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K5" t="n">
         <v>100</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004329257789743688</v>
+        <v>-0.0004783681595870716</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0002188758801361869</v>
+        <v>0.0004193756316958189</v>
       </c>
       <c r="N5" t="n">
-        <v>2.164628894871844e-05</v>
+        <v>-2.391840797935358e-05</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -752,28 +752,28 @@
         <v>0.1</v>
       </c>
       <c r="I6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K6" t="n">
         <v>100</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0004689964087649052</v>
+        <v>-0.0007023291922937522</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0003082555497178618</v>
+        <v>0.0005133820589206552</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.344982043824526e-05</v>
+        <v>-3.511645961468761e-05</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -806,28 +806,28 @@
         <v>0.1</v>
       </c>
       <c r="I7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K7" t="n">
         <v>100</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00168130237380639</v>
+        <v>-0.0009151818471197386</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0004266242106483605</v>
+        <v>0.0006528999296491682</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.40651186903195e-05</v>
+        <v>-4.575909235598693e-05</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -860,28 +860,28 @@
         <v>0.1</v>
       </c>
       <c r="I8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K8" t="n">
         <v>100</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.003178293531169752</v>
+        <v>-0.001117104927919099</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0005719321449715351</v>
+        <v>0.0008516869959018541</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0001589146765584876</v>
+        <v>-5.585524639595496e-05</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -908,13 +908,13 @@
         <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="H9" t="n">
         <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -925,17 +925,17 @@
         <v>100</v>
       </c>
       <c r="L9" t="n">
-        <v>9.589230885853124e-05</v>
+        <v>-0.001311381502804765</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0001268143692795872</v>
+        <v>0.001126921161797146</v>
       </c>
       <c r="N9" t="n">
-        <v>4.794615442926562e-06</v>
+        <v>-6.556907514023822e-05</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -962,13 +962,13 @@
         <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
         <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -979,17 +979,17 @@
         <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>7.045266467836341e-05</v>
+        <v>-0.001502399985171341</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0001621526761166208</v>
+        <v>0.001499706559066188</v>
       </c>
       <c r="N10" t="n">
-        <v>3.522633233918171e-06</v>
+        <v>-7.511999925856703e-05</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -1016,13 +1016,13 @@
         <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
         <v>0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1033,17 +1033,17 @@
         <v>100</v>
       </c>
       <c r="L11" t="n">
-        <v>2.833770930945448e-05</v>
+        <v>-0.00169271275757035</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0002207775236436406</v>
+        <v>0.001993243013997735</v>
       </c>
       <c r="N11" t="n">
-        <v>1.416885465472724e-06</v>
+        <v>-8.463563787851754e-05</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -1070,13 +1070,13 @@
         <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="H12" t="n">
         <v>0.1</v>
       </c>
       <c r="I12" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1087,17 +1087,17 @@
         <v>100</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.074858433975495e-05</v>
+        <v>-0.001881164054567974</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0003095372381649434</v>
+        <v>0.002622967906073476</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.537429216987748e-06</v>
+        <v>-9.405820272839868e-05</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -1124,13 +1124,13 @@
         <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
         <v>0.1</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1141,17 +1141,17 @@
         <v>100</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0001044936939356823</v>
+        <v>-0.002065766332522001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0004359391790877741</v>
+        <v>0.003379425394263444</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.224684696784117e-06</v>
+        <v>-0.0001032883166261001</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -1178,13 +1178,13 @@
         <v>0.5</v>
       </c>
       <c r="G14" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0.1</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1195,17 +1195,17 @@
         <v>100</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.0001896358671879882</v>
+        <v>-0.002251557952902621</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0006033377447356276</v>
+        <v>0.004229115477048032</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.481793359399412e-06</v>
+        <v>-0.0001125778976451311</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -1232,13 +1232,13 @@
         <v>0.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
         <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1249,17 +1249,17 @@
         <v>100</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0002847798624428964</v>
+        <v>-0.002451990466522035</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0008088341961758801</v>
+        <v>0.005161379235330389</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.423899312214482e-05</v>
+        <v>-0.0001225995233261018</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P15" t="n">
@@ -1286,34 +1286,34 @@
         <v>0.5</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
         <v>0.1</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>100</v>
       </c>
       <c r="L16" t="n">
-        <v>7.468213724399186e-05</v>
+        <v>-0.002674887968998579</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0001268143692795872</v>
+        <v>0.006234376010282524</v>
       </c>
       <c r="N16" t="n">
-        <v>3.734106862199593e-06</v>
+        <v>-0.000133744398449929</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -1340,34 +1340,34 @@
         <v>0.5</v>
       </c>
       <c r="G17" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="H17" t="n">
         <v>0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>100</v>
       </c>
       <c r="L17" t="n">
-        <v>8.190227237140277e-05</v>
+        <v>-0.0029107652281373</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0001621526761166208</v>
+        <v>0.007542367229251986</v>
       </c>
       <c r="N17" t="n">
-        <v>4.095113618570139e-06</v>
+        <v>-0.000145538261406865</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -1394,631 +1394,37 @@
         <v>0.5</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
         <v>0.1</v>
       </c>
       <c r="I18" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
+          <t>cos(phi_Dp)</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>100</v>
       </c>
       <c r="L18" t="n">
-        <v>7.379389622435869e-05</v>
+        <v>-0.003138120433778448</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0002207775236436406</v>
+        <v>0.009110715264989022</v>
       </c>
       <c r="N18" t="n">
-        <v>3.689694811217934e-06</v>
+        <v>-0.0001569060216889224</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>p</t>
+          <t>d</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="n">
-        <v>100</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>50</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>100</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5.706345144012611e-05</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.0003095372381649434</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.853172572006306e-06</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>100</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G20" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>50</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>100</v>
-      </c>
-      <c r="L20" t="n">
-        <v>3.732264475412179e-05</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.0004359391790877741</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.86613223770609e-06</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>100</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>50</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>100</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.870247617913582e-05</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.0006033377447356276</v>
-      </c>
-      <c r="N21" t="n">
-        <v>9.351238089567912e-07</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>100</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G22" t="n">
-        <v>5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>50</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>cos(phi_Dp)cos(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>100</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.109244658503162e-06</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.0008088341961758801</v>
-      </c>
-      <c r="N22" t="n">
-        <v>5.546223292515808e-08</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>100</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I23" t="n">
-        <v>50</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>100</v>
-      </c>
-      <c r="L23" t="n">
-        <v>-1.502516563208255e-05</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.0001268143692795872</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-7.512582816041277e-07</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>100</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>50</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>100</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-5.036671969959097e-07</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.0001621526761166208</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-2.518335984979549e-08</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>100</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G25" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>50</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>100</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.321069294837602e-05</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.0002207775236436406</v>
-      </c>
-      <c r="N25" t="n">
-        <v>6.605346474188011e-07</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>100</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>50</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>100</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2.638847732079456e-05</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.0003095372381649434</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.319423866039728e-06</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>100</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G27" t="n">
-        <v>4</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>50</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>100</v>
-      </c>
-      <c r="L27" t="n">
-        <v>3.93166388068682e-05</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.0004359391790877741</v>
-      </c>
-      <c r="N27" t="n">
-        <v>1.96583194034341e-06</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C28" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>100</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>50</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>100</v>
-      </c>
-      <c r="L28" t="n">
-        <v>5.181303201754629e-05</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.0006033377447356276</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.590651600877315e-06</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="C29" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" t="n">
-        <v>100</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>50</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>sin(phi_Dp)sin(phi_kp)</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>100</v>
-      </c>
-      <c r="L29" t="n">
-        <v>6.431865751913868e-05</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.0008088341961758801</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.215932875956934e-06</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>p</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
         <v>1</v>
       </c>
     </row>
